--- a/Excel/Datas/buff.xlsx
+++ b/Excel/Datas/buff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="buff_table" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -47,6 +47,9 @@
     <t>only_in_battle</t>
   </si>
   <si>
+    <t>desc</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
     <t>是否只在战斗中存在</t>
   </si>
   <si>
+    <t>效果描述</t>
+  </si>
+  <si>
     <t>测试0</t>
   </si>
   <si>
@@ -90,6 +96,75 @@
   </si>
   <si>
     <t>永久</t>
+  </si>
+  <si>
+    <t>易损</t>
+  </si>
+  <si>
+    <t>敌方单体</t>
+  </si>
+  <si>
+    <t>即时</t>
+  </si>
+  <si>
+    <t>受到高额伤害可触发，此次伤害改为2倍。</t>
+  </si>
+  <si>
+    <t>暴虐</t>
+  </si>
+  <si>
+    <t>每次攻击伤害提升25%。</t>
+  </si>
+  <si>
+    <t>吸血</t>
+  </si>
+  <si>
+    <t>攻击后恢复生命，等同于此次攻击造成伤害的25%。</t>
+  </si>
+  <si>
+    <t>肉质</t>
+  </si>
+  <si>
+    <t>受到的攻击伤害降低25%。</t>
+  </si>
+  <si>
+    <t>寄生</t>
+  </si>
+  <si>
+    <t>敌方单体;我方全体</t>
+  </si>
+  <si>
+    <t>回合结束可触发，受到1点伤害（此伤害无视防御和适应），并且给所有敌方植物分别恢复等量生命。最多叠加三层。</t>
+  </si>
+  <si>
+    <t>灼伤</t>
+  </si>
+  <si>
+    <t>回合结束可触发，受到等同于最大生命值5%的伤害。此伤害无视防御和适应。</t>
+  </si>
+  <si>
+    <t>储藏</t>
+  </si>
+  <si>
+    <t>当一个己方怪兽的当前生命低于其最大生命的10%时，消耗一层储藏效果，并使其恢复最大生命20%的生命。最多叠加三层。</t>
+  </si>
+  <si>
+    <t>升级</t>
+  </si>
+  <si>
+    <t>当道具卡高速升级，装甲升级，和重组升级对机械怪兽生效时，该机械怪兽会获得一层升级效果，并且该升级效果会储存对应的道具卡效果。</t>
+  </si>
+  <si>
+    <t>神经毒素</t>
+  </si>
+  <si>
+    <t>攻击时触发，有20%的几率使此次攻击失败。受到攻击时，若此次攻击造成高额伤害，消耗一层神经毒素效果，并额外受到等同于最大生命10%的伤害。最多叠加一层。</t>
+  </si>
+  <si>
+    <t>高额伤害</t>
+  </si>
+  <si>
+    <t>一种特殊的攻击类型，能够触发某些效果。</t>
   </si>
 </sst>
 </file>
@@ -102,7 +177,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,6 +188,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -468,7 +550,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -500,6 +582,21 @@
       </right>
       <top/>
       <bottom style="medium">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
@@ -635,147 +732,162 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1103,15 +1215,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="5" width="18.7410714285714" customWidth="1"/>
-    <col min="6" max="6" width="21.5803571428571" customWidth="1"/>
+    <col min="3" max="5" width="18.7416666666667" customWidth="1"/>
+    <col min="6" max="6" width="21.5833333333333" customWidth="1"/>
+    <col min="7" max="7" width="71.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1129,6 +1242,9 @@
       </c>
       <c r="F1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1140,142 +1256,288 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" ht="14.75" spans="2:6">
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="2:5">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="2:5">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="2:5">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="2:5">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="2:5">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="2:5">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="2:5">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="5"/>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="5"/>
+    <row r="7" ht="14.75" spans="2:7">
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="14.75" spans="2:7">
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="14.75" spans="2:7">
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="14.75" spans="2:7">
+      <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" ht="14.75" spans="2:7">
+      <c r="B11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" ht="14.75" spans="2:7">
+      <c r="B12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" ht="14.75" spans="2:7">
+      <c r="B13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" ht="14.75" spans="2:7">
+      <c r="B14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" ht="14.75" spans="2:7">
+      <c r="B15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" ht="14.75" spans="2:7">
+      <c r="B16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" ht="14.75" spans="2:5">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" ht="14.75" spans="2:2">
+      <c r="B18" s="10"/>
+    </row>
+    <row r="19" ht="14.75" spans="2:2">
+      <c r="B19" s="10"/>
+    </row>
+    <row r="20" ht="14.75" spans="2:2">
+      <c r="B20" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/Datas/buff.xlsx
+++ b/Excel/Datas/buff.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -104,7 +104,7 @@
     <t>敌方单体</t>
   </si>
   <si>
-    <t>即时</t>
+    <t>倒计时</t>
   </si>
   <si>
     <t>受到高额伤害可触发，此次伤害改为2倍。</t>
@@ -129,9 +129,6 @@
   </si>
   <si>
     <t>寄生</t>
-  </si>
-  <si>
-    <t>敌方单体;我方全体</t>
   </si>
   <si>
     <t>回合结束可触发，受到1点伤害（此伤害无视防御和适应），并且给所有敌方植物分别恢复等量生命。最多叠加三层。</t>
@@ -862,7 +859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -883,9 +880,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1404,13 +1398,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" ht="14.75" spans="2:7">
+    <row r="11" spans="2:7">
       <c r="B11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>34</v>
-      </c>
+      <c r="C11" s="5"/>
       <c r="D11" s="6" t="s">
         <v>25</v>
       </c>
@@ -1421,12 +1413,12 @@
         <v>1</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" ht="14.75" spans="2:7">
       <c r="B12" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>24</v>
@@ -1435,18 +1427,18 @@
         <v>25</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" ht="14.75" spans="2:7">
       <c r="B13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>21</v>
@@ -1455,18 +1447,18 @@
         <v>25</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" ht="14.75" spans="2:7">
       <c r="B14" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>21</v>
@@ -1475,18 +1467,18 @@
         <v>22</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="14.75" spans="2:7">
       <c r="B15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>24</v>
@@ -1495,18 +1487,18 @@
         <v>25</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
       </c>
       <c r="G15" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" ht="14.75" spans="2:7">
+      <c r="B16" s="4" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="16" ht="14.75" spans="2:7">
-      <c r="B16" s="9" t="s">
-        <v>44</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>24</v>
@@ -1514,14 +1506,14 @@
       <c r="D16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>44</v>
+      <c r="E16" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" ht="14.75" spans="2:5">
@@ -1531,13 +1523,13 @@
       <c r="E17" s="6"/>
     </row>
     <row r="18" ht="14.75" spans="2:2">
-      <c r="B18" s="10"/>
+      <c r="B18" s="9"/>
     </row>
     <row r="19" ht="14.75" spans="2:2">
-      <c r="B19" s="10"/>
+      <c r="B19" s="9"/>
     </row>
     <row r="20" ht="14.75" spans="2:2">
-      <c r="B20" s="10"/>
+      <c r="B20" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/Datas/buff.xlsx
+++ b/Excel/Datas/buff.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D361459A-1BC9-4215-985A-69AB7E072061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="buff_table" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -89,9 +93,6 @@
     <t>效果描述</t>
   </si>
   <si>
-    <t>测试0</t>
-  </si>
-  <si>
     <t>我方单体</t>
   </si>
   <si>
@@ -162,19 +163,17 @@
   </si>
   <si>
     <t>一种特殊的攻击类型，能够触发某些效果。</t>
+  </si>
+  <si>
+    <t>下次攻击伤害三倍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,151 +196,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,204 +219,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799676503799554"/>
+        <fgColor theme="5" tint="0.79964598529007846"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399670400097659"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39963988158818325"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -613,263 +296,21 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -884,68 +325,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00F43308"/>
-      <color rgb="00FF8680"/>
+      <color rgb="FFF43308"/>
+      <color rgb="FFFF8680"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1203,22 +603,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="5" width="18.7416666666667" customWidth="1"/>
-    <col min="6" max="6" width="21.5833333333333" customWidth="1"/>
-    <col min="7" max="7" width="71.9166666666667" customWidth="1"/>
+    <col min="3" max="5" width="18.75" customWidth="1"/>
+    <col min="6" max="6" width="21.625" customWidth="1"/>
+    <col min="7" max="7" width="71.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1241,7 +641,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1250,7 +650,7 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,7 +673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1282,7 +682,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -1303,236 +703,236 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="14.75" spans="2:6">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="14.75" spans="2:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" ht="14.75" spans="2:7">
-      <c r="B8" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="C8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" ht="14.75" spans="2:7">
-      <c r="B9" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="C9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" ht="14.75" spans="2:7">
-      <c r="B10" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="C10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="4" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="12" ht="14.75" spans="2:7">
-      <c r="B12" s="4" t="s">
-        <v>35</v>
-      </c>
       <c r="C12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" ht="14.75" spans="2:7">
-      <c r="B13" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="C13" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
       </c>
       <c r="G13" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" ht="14.75" spans="2:7">
-      <c r="B14" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="C14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" ht="14.75" spans="2:7">
-      <c r="B15" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="C15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="E15" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
       </c>
       <c r="G15" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="16" ht="14.75" spans="2:7">
-      <c r="B16" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="C16" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" ht="14.75" spans="2:5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" ht="14.75" spans="2:2">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="9"/>
     </row>
-    <row r="19" ht="14.75" spans="2:2">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="9"/>
     </row>
-    <row r="20" ht="14.75" spans="2:2">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="9"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/Datas/buff.xlsx
+++ b/Excel/Datas/buff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D361459A-1BC9-4215-985A-69AB7E072061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB15349E-1433-40B8-BF8D-2F21B0E4FA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -39,12 +39,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>target_type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -60,12 +54,6 @@
     <t>BuffEnum</t>
   </si>
   <si>
-    <t>BuffTargetTypeEnum</t>
-  </si>
-  <si>
-    <t>BuffType</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -81,9 +69,6 @@
     <t>ID</t>
   </si>
   <si>
-    <t>目标</t>
-  </si>
-  <si>
     <t>名字(不填从id解析)</t>
   </si>
   <si>
@@ -93,19 +78,7 @@
     <t>效果描述</t>
   </si>
   <si>
-    <t>我方单体</t>
-  </si>
-  <si>
-    <t>永久</t>
-  </si>
-  <si>
     <t>易损</t>
-  </si>
-  <si>
-    <t>敌方单体</t>
-  </si>
-  <si>
-    <t>倒计时</t>
   </si>
   <si>
     <t>受到高额伤害可触发，此次伤害改为2倍。</t>
@@ -300,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -309,9 +282,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -609,16 +579,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="5" width="18.75" customWidth="1"/>
-    <col min="6" max="6" width="21.625" customWidth="1"/>
-    <col min="7" max="7" width="71.875" customWidth="1"/>
+    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="4" max="4" width="21.625" customWidth="1"/>
+    <col min="5" max="5" width="71.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -628,308 +598,222 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F5" t="s">
+      <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G5" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="C9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="3" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" t="b">
+      <c r="C10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="4" t="s">
+      <c r="E10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="5" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="C11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="b">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="b">
         <v>1</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="4" t="s">
+      <c r="E12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" t="b">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="b">
         <v>0</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="4" t="s">
+      <c r="E14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7" t="s">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="4" t="s">
+      <c r="C15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" t="b">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" t="b">
         <v>1</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="4" t="s">
+      <c r="E16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B18" s="9"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="9"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B20" s="9"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B18" s="8"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B19" s="8"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B20" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
